--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>3</v>
+      </c>
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>22.222222222222</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>-28.571428571428</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.428571428571</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.970588235294</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15">
         <v>5</v>
       </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
       <c r="E17" s="14">
-        <v>-16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>27.777777777777</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K17" s="14">
-        <v>26.923076923076</v>
+        <v>19.354838709677</v>
       </c>
       <c r="L17" s="14">
-        <v>-2.941176470588</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="M17" s="14">
-        <v>32</v>
+        <v>42.307692307692</v>
       </c>
       <c r="N17" s="14">
-        <v>73.684210526315</v>
+        <v>68.181818181818</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-25</v>
+        <v>-45</v>
       </c>
       <c r="L18" s="14">
-        <v>-40</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M18" s="14">
-        <v>-83.018867924528</v>
+        <v>-81.034482758620</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.120689655172</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
         <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-18.181818181818</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F19" s="15">
         <v>40</v>
@@ -1075,22 +1075,22 @@
         <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="J19" s="15">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K19" s="14">
-        <v>16</v>
+        <v>19.672131147541</v>
       </c>
       <c r="L19" s="14">
-        <v>-41.414141414141</v>
+        <v>-31.132075471698</v>
       </c>
       <c r="M19" s="14">
-        <v>18.367346938775</v>
+        <v>32.727272727272</v>
       </c>
       <c r="N19" s="14">
-        <v>-4.918032786885</v>
+        <v>-1.351351351351</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
-      </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>150</v>
+        <v>6</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G20" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>76.923076923076</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J20" s="15">
         <v>21</v>
       </c>
       <c r="K20" s="14">
-        <v>42.857142857142</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L20" s="14">
-        <v>-23.076923076923</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M20" s="14">
-        <v>-3.225806451612</v>
+        <v>12.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.610837438423</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.347826086956</v>
+        <v>11.538461538461</v>
       </c>
       <c r="F21" s="17">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>16.666666666666</v>
+        <v>8.791208791208</v>
       </c>
       <c r="I21" s="17">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="J21" s="17">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="K21" s="18">
-        <v>18.548387096774</v>
+        <v>18</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.665071770334</v>
+        <v>-25.941422594142</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.808510638297</v>
+        <v>-12.376237623762</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.867132867132</v>
+        <v>-82.139253279515</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L22" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>35.714285714285</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="F24" s="15">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G24" s="15">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H24" s="14">
-        <v>-2.857142857142</v>
+        <v>-1.041666666666</v>
       </c>
       <c r="I24" s="15">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="J24" s="15">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="K24" s="14">
-        <v>-3.787878787878</v>
+        <v>-3.870967741935</v>
       </c>
       <c r="L24" s="14">
-        <v>-22.085889570552</v>
+        <v>-19.892473118279</v>
       </c>
       <c r="M24" s="14">
-        <v>10.434782608695</v>
+        <v>6.428571428571</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>28.571428571428</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F25" s="15">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G25" s="15">
         <v>40</v>
       </c>
       <c r="H25" s="14">
-        <v>-10</v>
+        <v>-27.5</v>
       </c>
       <c r="I25" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J25" s="15">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="K25" s="14">
-        <v>-21.153846153846</v>
+        <v>-30.158730158730</v>
       </c>
       <c r="L25" s="14">
-        <v>-14.583333333333</v>
+        <v>-22.807017543859</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>13</v>
+      </c>
+      <c r="D26" s="15">
         <v>9</v>
       </c>
-      <c r="D26" s="15">
-        <v>6</v>
-      </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H26" s="14">
-        <v>2.857142857142</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J26" s="15">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K26" s="14">
-        <v>12.244897959183</v>
+        <v>15.517241379310</v>
       </c>
       <c r="L26" s="14">
-        <v>14.583333333333</v>
+        <v>13.559322033898</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.675675675675</v>
+        <v>-27.173913043478</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
         <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F28" s="15">
-        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
         <v>6</v>
@@ -1453,7 +1453,7 @@
         <v>20</v>
       </c>
       <c r="L28" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="14">
         <v>-100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>-100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="14">
         <v>-100</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>-100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,38 +892,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
         <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
         <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>28.571428571428</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L16" s="14">
-        <v>-35.714285714285</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="M16" s="14">
-        <v>-37.931034482758</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.461538461538</v>
+        <v>-85.555555555555</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="15">
         <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>15.789473684210</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J17" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K17" s="14">
-        <v>19.354838709677</v>
+        <v>13.888888888888</v>
       </c>
       <c r="L17" s="14">
-        <v>-9.756097560975</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="M17" s="14">
-        <v>42.307692307692</v>
+        <v>41.379310344827</v>
       </c>
       <c r="N17" s="14">
-        <v>68.181818181818</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>-45</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L18" s="14">
-        <v>-42.105263157894</v>
+        <v>-48</v>
       </c>
       <c r="M18" s="14">
-        <v>-81.034482758620</v>
+        <v>-81.690140845070</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.833333333333</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>36.363636363636</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" s="15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H19" s="14">
+        <v>13.157894736842</v>
+      </c>
+      <c r="I19" s="15">
+        <v>83</v>
+      </c>
+      <c r="J19" s="15">
+        <v>70</v>
+      </c>
+      <c r="K19" s="14">
+        <v>18.571428571428</v>
+      </c>
+      <c r="L19" s="14">
+        <v>-28.448275862069</v>
+      </c>
+      <c r="M19" s="14">
+        <v>33.870967741935</v>
+      </c>
+      <c r="N19" s="14">
         <v>0</v>
-      </c>
-      <c r="I19" s="15">
-        <v>73</v>
-      </c>
-      <c r="J19" s="15">
-        <v>61</v>
-      </c>
-      <c r="K19" s="14">
-        <v>19.672131147541</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-31.132075471698</v>
-      </c>
-      <c r="M19" s="14">
-        <v>32.727272727272</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-1.351351351351</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="15">
         <v>6</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>58.333333333333</v>
+        <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J20" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K20" s="14">
-        <v>71.428571428571</v>
+        <v>82.608695652173</v>
       </c>
       <c r="L20" s="14">
-        <v>-18.181818181818</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M20" s="14">
-        <v>12.5</v>
+        <v>23.529411764705</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.307692307692</v>
+        <v>-92.045454545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>11.538461538461</v>
+        <v>63.157894736842</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G21" s="17">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>8.791208791208</v>
+        <v>22.352941176470</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="J21" s="17">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="K21" s="18">
-        <v>18</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.941422594142</v>
+        <v>-22.676579925650</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.376237623762</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.139253279515</v>
+        <v>-81.494661921708</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
         <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-4.347826086956</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G24" s="15">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H24" s="14">
-        <v>-1.041666666666</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I24" s="15">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="J24" s="15">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="K24" s="14">
-        <v>-3.870967741935</v>
+        <v>-2.793296089385</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.892473118279</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="M24" s="14">
-        <v>6.428571428571</v>
+        <v>6.097560975609</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-72.727272727272</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="15">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G25" s="15">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H25" s="14">
-        <v>-27.5</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="I25" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J25" s="15">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.158730158730</v>
+        <v>-31.506849315068</v>
       </c>
       <c r="L25" s="14">
-        <v>-22.807017543859</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>44.444444444444</v>
+        <v>160</v>
       </c>
       <c r="F26" s="15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>33.333333333333</v>
+        <v>45.161290322580</v>
       </c>
       <c r="I26" s="15">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J26" s="15">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K26" s="14">
-        <v>15.517241379310</v>
+        <v>25.396825396825</v>
       </c>
       <c r="L26" s="14">
-        <v>13.559322033898</v>
+        <v>3.947368421052</v>
       </c>
       <c r="M26" s="14">
-        <v>-27.173913043478</v>
+        <v>-25.471698113207</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>-50</v>
+      </c>
+      <c r="I27" s="15">
         <v>3</v>
       </c>
-      <c r="H27" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I27" s="15">
-        <v>2</v>
-      </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,29 +1428,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="15">
         <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
         <v>100</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="15">
         <v>1</v>
       </c>
       <c r="K29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,26 +1557,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
+        <v>1</v>
+      </c>
+      <c r="J31" s="15">
         <v>2</v>
       </c>
-      <c r="H31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="15">
-        <v>4</v>
-      </c>
       <c r="K31" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>8</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>200</v>
       </c>
       <c r="F16" s="15">
+        <v>16</v>
+      </c>
+      <c r="G16" s="15">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
+        <v>29</v>
+      </c>
+      <c r="J16" s="15">
         <v>15</v>
       </c>
-      <c r="G16" s="15">
-        <v>6</v>
-      </c>
-      <c r="H16" s="14">
-        <v>150</v>
-      </c>
-      <c r="I16" s="15">
-        <v>26</v>
-      </c>
-      <c r="J16" s="15">
-        <v>14</v>
-      </c>
       <c r="K16" s="14">
-        <v>85.714285714285</v>
+        <v>93.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-21.212121212121</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M16" s="14">
-        <v>-23.529411764705</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.555555555555</v>
+        <v>-85.128205128205</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
-        <v>5.263157894736</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J17" s="15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K17" s="14">
-        <v>13.888888888888</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L17" s="14">
-        <v>-4.651162790697</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="M17" s="14">
-        <v>41.379310344827</v>
+        <v>53.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>64</v>
+        <v>58.620689655172</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-53.846153846153</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" s="14">
-        <v>-40.909090909090</v>
+        <v>-28</v>
       </c>
       <c r="L18" s="14">
-        <v>-48</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-81.690140845070</v>
+        <v>-77.215189873417</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.652173913043</v>
+        <v>-94.578313253012</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1066,31 +1066,31 @@
         <v>22.222222222222</v>
       </c>
       <c r="F19" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>13.157894736842</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J19" s="15">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K19" s="14">
-        <v>18.571428571428</v>
+        <v>20.253164556962</v>
       </c>
       <c r="L19" s="14">
-        <v>-28.448275862069</v>
+        <v>-30.147058823529</v>
       </c>
       <c r="M19" s="14">
-        <v>33.870967741935</v>
+        <v>41.791044776119</v>
       </c>
       <c r="N19" s="14">
-        <v>0</v>
+        <v>-2.061855670103</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G20" s="15">
         <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J20" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K20" s="14">
-        <v>82.608695652173</v>
+        <v>80</v>
       </c>
       <c r="L20" s="14">
-        <v>-17.647058823529</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="14">
-        <v>23.529411764705</v>
+        <v>21.621621621621</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.045454545454</v>
+        <v>-92.487479131886</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>63.157894736842</v>
+        <v>20.833333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>22.352941176470</v>
+        <v>19.565217391304</v>
       </c>
       <c r="I21" s="17">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="J21" s="17">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="K21" s="18">
-        <v>23.076923076923</v>
+        <v>23.316062176165</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.676579925650</v>
+        <v>-24.683544303797</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.344827586206</v>
+        <v>-5.928853754940</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.494661921708</v>
+        <v>-81.141045958795</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>150</v>
       </c>
       <c r="L22" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>4.166666666666</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F24" s="15">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G24" s="15">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H24" s="14">
-        <v>-3.448275862068</v>
+        <v>-6.25</v>
       </c>
       <c r="I24" s="15">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J24" s="15">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K24" s="14">
-        <v>-2.793296089385</v>
+        <v>-8.080808080808</v>
       </c>
       <c r="L24" s="14">
-        <v>-25.641025641025</v>
+        <v>-31.060606060606</v>
       </c>
       <c r="M24" s="14">
-        <v>6.097560975609</v>
+        <v>4</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
         <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-40</v>
+        <v>-90</v>
       </c>
       <c r="F25" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G25" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H25" s="14">
-        <v>-34.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J25" s="15">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.506849315068</v>
+        <v>-38.554216867469</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.076923076923</v>
+        <v>-32</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,13 +1344,13 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>160</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="15">
         <v>45</v>
@@ -1362,19 +1362,19 @@
         <v>45.161290322580</v>
       </c>
       <c r="I26" s="15">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J26" s="15">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="K26" s="14">
-        <v>25.396825396825</v>
+        <v>20.270270270270</v>
       </c>
       <c r="L26" s="14">
-        <v>3.947368421052</v>
+        <v>-1.111111111111</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.471698113207</v>
+        <v>-25.210084033613</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
+        <v>100</v>
+      </c>
+      <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
         <v>0</v>
       </c>
-      <c r="F27" s="15">
-        <v>2</v>
-      </c>
-      <c r="G27" s="15">
-        <v>4</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-50</v>
-      </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-40</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>1</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="15">
         <v>1</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,35 +892,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
       <c r="E15" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="15">
         <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L15" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M15" s="14">
         <v>150</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
         <v>16</v>
       </c>
       <c r="G16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="I16" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
-        <v>93.333333333333</v>
+        <v>82.352941176470</v>
       </c>
       <c r="L16" s="14">
-        <v>-17.142857142857</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="M16" s="14">
-        <v>-23.684210526315</v>
+        <v>-22.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.128205128205</v>
+        <v>-85.238095238095</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-37.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F17" s="15">
         <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H17" s="14">
-        <v>-33.333333333333</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I17" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J17" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K17" s="14">
-        <v>4.545454545454</v>
+        <v>8.510638297872</v>
       </c>
       <c r="L17" s="14">
-        <v>-2.127659574468</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="M17" s="14">
-        <v>53.333333333333</v>
+        <v>64.516129032258</v>
       </c>
       <c r="N17" s="14">
-        <v>58.620689655172</v>
+        <v>34.210526315789</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K18" s="14">
-        <v>-28</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L18" s="14">
-        <v>-48.571428571428</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M18" s="14">
-        <v>-77.215189873417</v>
+        <v>-75</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.578313253012</v>
+        <v>-94.195250659630</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>13</v>
+      </c>
+      <c r="D19" s="15">
         <v>11</v>
       </c>
-      <c r="D19" s="15">
-        <v>9</v>
-      </c>
       <c r="E19" s="14">
-        <v>22.222222222222</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G19" s="15">
         <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>12.5</v>
+        <v>22.5</v>
       </c>
       <c r="I19" s="15">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J19" s="15">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K19" s="14">
-        <v>20.253164556962</v>
+        <v>20</v>
       </c>
       <c r="L19" s="14">
-        <v>-30.147058823529</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="M19" s="14">
-        <v>41.791044776119</v>
+        <v>54.285714285714</v>
       </c>
       <c r="N19" s="14">
-        <v>-2.061855670103</v>
+        <v>-2.702702702702</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E20" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>233.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J20" s="15">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K20" s="14">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="L20" s="14">
-        <v>-25</v>
+        <v>-17.460317460317</v>
       </c>
       <c r="M20" s="14">
-        <v>21.621621621621</v>
+        <v>15.555555555555</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.487479131886</v>
+        <v>-92.227204783258</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>31</v>
+      </c>
+      <c r="D21" s="17">
         <v>29</v>
       </c>
-      <c r="D21" s="17">
-        <v>24</v>
-      </c>
       <c r="E21" s="18">
-        <v>20.833333333333</v>
+        <v>6.896551724137</v>
       </c>
       <c r="F21" s="17">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>19.565217391304</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="J21" s="17">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="K21" s="18">
-        <v>23.316062176165</v>
+        <v>21.171171171171</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.683544303797</v>
+        <v>-22.701149425287</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.928853754940</v>
+        <v>-2.536231884057</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.141045958795</v>
+        <v>-81.016231474947</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-47.368421052631</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G24" s="15">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H24" s="14">
-        <v>-6.25</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="I24" s="15">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="J24" s="15">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="K24" s="14">
-        <v>-8.080808080808</v>
+        <v>-3.738317757009</v>
       </c>
       <c r="L24" s="14">
-        <v>-31.060606060606</v>
+        <v>-28.222996515679</v>
       </c>
       <c r="M24" s="14">
-        <v>4</v>
+        <v>7.853403141361</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H25" s="14">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I25" s="15">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J25" s="15">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K25" s="14">
-        <v>-38.554216867469</v>
+        <v>-35.164835164835</v>
       </c>
       <c r="L25" s="14">
-        <v>-32</v>
+        <v>-30.588235294117</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-9.090909090909</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H26" s="14">
-        <v>45.161290322580</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I26" s="15">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J26" s="15">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K26" s="14">
-        <v>20.270270270270</v>
+        <v>19.277108433734</v>
       </c>
       <c r="L26" s="14">
-        <v>-1.111111111111</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.210084033613</v>
+        <v>-25.563909774436</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
       <c r="E27" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-16.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="L27" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="15">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
         <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15">
-        <v>6</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>6</v>
@@ -1453,7 +1453,7 @@
         <v>-25</v>
       </c>
       <c r="L28" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14">
+        <v>-20</v>
+      </c>
+      <c r="I15" s="15">
+        <v>6</v>
+      </c>
+      <c r="J15" s="15">
+        <v>8</v>
+      </c>
+      <c r="K15" s="14">
         <v>-25</v>
       </c>
-      <c r="I15" s="15">
-        <v>5</v>
-      </c>
-      <c r="J15" s="15">
-        <v>7</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-28.571428571428</v>
-      </c>
       <c r="L15" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>220</v>
+        <v>142.857142857143</v>
       </c>
       <c r="I16" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>82.352941176470</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-18.421052631578</v>
+        <v>-12.5</v>
       </c>
       <c r="M16" s="14">
-        <v>-22.5</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.238095238095</v>
+        <v>-84.162895927601</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
+        <v>14.285714285714</v>
+      </c>
+      <c r="F17" s="15">
+        <v>22</v>
+      </c>
+      <c r="G17" s="15">
+        <v>23</v>
+      </c>
+      <c r="H17" s="14">
+        <v>-4.347826086956</v>
+      </c>
+      <c r="I17" s="15">
+        <v>60</v>
+      </c>
+      <c r="J17" s="15">
+        <v>54</v>
+      </c>
+      <c r="K17" s="14">
+        <v>11.111111111111</v>
+      </c>
+      <c r="L17" s="14">
+        <v>7.142857142857</v>
+      </c>
+      <c r="M17" s="14">
         <v>66.666666666666</v>
       </c>
-      <c r="F17" s="15">
-        <v>16</v>
-      </c>
-      <c r="G17" s="15">
-        <v>21</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-23.809523809523</v>
-      </c>
-      <c r="I17" s="15">
-        <v>51</v>
-      </c>
-      <c r="J17" s="15">
-        <v>47</v>
-      </c>
-      <c r="K17" s="14">
-        <v>8.510638297872</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-3.773584905660</v>
-      </c>
-      <c r="M17" s="14">
-        <v>64.516129032258</v>
-      </c>
       <c r="N17" s="14">
-        <v>34.210526315789</v>
+        <v>39.534883720930</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-23.529411764705</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K18" s="14">
-        <v>-24.137931034482</v>
+        <v>-15.625</v>
       </c>
       <c r="L18" s="14">
-        <v>-47.619047619047</v>
+        <v>-38.636363636363</v>
       </c>
       <c r="M18" s="14">
-        <v>-75</v>
+        <v>-69.662921348314</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.195250659630</v>
+        <v>-93.446601941747</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
         <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="15">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G19" s="15">
         <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J19" s="15">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K19" s="14">
-        <v>20</v>
+        <v>16.831683168316</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.027027027027</v>
+        <v>-23.870967741935</v>
       </c>
       <c r="M19" s="14">
-        <v>54.285714285714</v>
+        <v>55.263157894736</v>
       </c>
       <c r="N19" s="14">
-        <v>-2.702702702702</v>
+        <v>0.854700854700</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="14">
         <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I20" s="15">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J20" s="15">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K20" s="14">
-        <v>62.5</v>
+        <v>48.780487804878</v>
       </c>
       <c r="L20" s="14">
-        <v>-17.460317460317</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>15.555555555555</v>
+        <v>27.083333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.227204783258</v>
+        <v>-91.492329149232</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>6.896551724137</v>
+        <v>2.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H21" s="18">
-        <v>21.428571428571</v>
+        <v>20.560747663551</v>
       </c>
       <c r="I21" s="17">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="J21" s="17">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="K21" s="18">
-        <v>21.171171171171</v>
+        <v>19.455252918287</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.701149425287</v>
+        <v>-17.027027027027</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.536231884057</v>
+        <v>3.020134228187</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.016231474947</v>
+        <v>-79.829172141918</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="14">
-        <v>62.5</v>
+        <v>64.705882352941</v>
       </c>
       <c r="F24" s="15">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G24" s="15">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H24" s="14">
-        <v>-2.439024390243</v>
+        <v>13.157894736842</v>
       </c>
       <c r="I24" s="15">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="J24" s="15">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="K24" s="14">
-        <v>-3.738317757009</v>
+        <v>0.865800865800</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.222996515679</v>
+        <v>-24.595469255663</v>
       </c>
       <c r="M24" s="14">
-        <v>7.853403141361</v>
+        <v>11.483253588516</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" s="15">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H25" s="14">
-        <v>-53.846153846153</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="I25" s="15">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J25" s="15">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K25" s="14">
-        <v>-35.164835164835</v>
+        <v>-36</v>
       </c>
       <c r="L25" s="14">
-        <v>-30.588235294117</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>11.111111111111</v>
+        <v>150</v>
       </c>
       <c r="F26" s="15">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G26" s="15">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>35.294117647058</v>
+        <v>44.827586206896</v>
       </c>
       <c r="I26" s="15">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J26" s="15">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K26" s="14">
-        <v>19.277108433734</v>
+        <v>24.137931034482</v>
       </c>
       <c r="L26" s="14">
         <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.563909774436</v>
+        <v>-28.476821192053</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1428,17 +1428,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1447,13 +1447,13 @@
         <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="14">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="15">
         <v>4</v>
       </c>
-      <c r="G15" s="15">
-        <v>5</v>
-      </c>
       <c r="H15" s="14">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="15">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>142.857142857143</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="15">
         <v>35</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K16" s="14">
-        <v>66.666666666666</v>
+        <v>34.615384615384</v>
       </c>
       <c r="L16" s="14">
-        <v>-12.5</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="M16" s="14">
-        <v>-25.531914893617</v>
+        <v>-33.962264150943</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.162895927601</v>
+        <v>-85.232067510548</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>10</v>
+      </c>
+      <c r="D17" s="15">
         <v>8</v>
       </c>
-      <c r="D17" s="15">
-        <v>7</v>
-      </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H17" s="14">
-        <v>-4.347826086956</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I17" s="15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J17" s="15">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K17" s="14">
-        <v>11.111111111111</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L17" s="14">
-        <v>7.142857142857</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M17" s="14">
-        <v>66.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N17" s="14">
-        <v>39.534883720930</v>
+        <v>55.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E18" s="14">
-        <v>33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="15">
         <v>16</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H18" s="14">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J18" s="15">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K18" s="14">
-        <v>-15.625</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.636363636363</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="M18" s="14">
-        <v>-69.662921348314</v>
+        <v>-71</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.446601941747</v>
+        <v>-93.394077448747</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-9.090909090909</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G19" s="15">
         <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>12.5</v>
+        <v>22.5</v>
       </c>
       <c r="I19" s="15">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J19" s="15">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="K19" s="14">
-        <v>16.831683168316</v>
+        <v>21.818181818181</v>
       </c>
       <c r="L19" s="14">
-        <v>-23.870967741935</v>
+        <v>-21.176470588235</v>
       </c>
       <c r="M19" s="14">
-        <v>55.263157894736</v>
+        <v>59.523809523809</v>
       </c>
       <c r="N19" s="14">
-        <v>0.854700854700</v>
+        <v>4.6875</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G20" s="15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H20" s="14">
-        <v>25</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I20" s="15">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J20" s="15">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K20" s="14">
-        <v>48.780487804878</v>
+        <v>30.612244897959</v>
       </c>
       <c r="L20" s="14">
-        <v>-12.857142857142</v>
+        <v>-14.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>27.083333333333</v>
+        <v>10.344827586206</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.492329149232</v>
+        <v>-91.784338896020</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>2.857142857142</v>
+        <v>-32.5</v>
       </c>
       <c r="F21" s="17">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G21" s="17">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H21" s="18">
-        <v>20.560747663551</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="J21" s="17">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="K21" s="18">
-        <v>19.455252918287</v>
+        <v>13.804713804713</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.027027027027</v>
+        <v>-15.920398009950</v>
       </c>
       <c r="M21" s="18">
-        <v>3.020134228187</v>
+        <v>-1.169590643274</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.829172141918</v>
+        <v>-79.390243902439</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,31 +1183,31 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>64.705882352941</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="F24" s="15">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" s="15">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H24" s="14">
-        <v>13.157894736842</v>
+        <v>2.409638554216</v>
       </c>
       <c r="I24" s="15">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="J24" s="15">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="K24" s="14">
-        <v>0.865800865800</v>
+        <v>-2.671755725190</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.595469255663</v>
+        <v>-22.492401215805</v>
       </c>
       <c r="M24" s="14">
-        <v>11.483253588516</v>
+        <v>8.974358974358</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-55.555555555555</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F25" s="15">
         <v>20</v>
       </c>
       <c r="G25" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H25" s="14">
-        <v>-45.945945945945</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I25" s="15">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J25" s="15">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="K25" s="14">
-        <v>-36</v>
+        <v>-36.936936936936</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.089887640449</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>150</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F26" s="15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>44.827586206896</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="15">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J26" s="15">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K26" s="14">
-        <v>24.137931034482</v>
+        <v>20.408163265306</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>-7.8125</v>
       </c>
       <c r="M26" s="14">
-        <v>-28.476821192053</v>
+        <v>-29.341317365269</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
         <v>4</v>
       </c>
-      <c r="G27" s="15">
-        <v>5</v>
-      </c>
       <c r="H27" s="14">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F28" s="15">
+        <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>-40</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L28" s="14">
         <v>0</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,35 +895,35 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
       </c>
       <c r="J15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
         <v>20</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
         <v>-25</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-80</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-16.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I16" s="15">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="14">
-        <v>34.615384615384</v>
+        <v>41.379310344827</v>
       </c>
       <c r="L16" s="14">
-        <v>-18.604651162790</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="M16" s="14">
-        <v>-33.962264150943</v>
+        <v>-25.454545454545</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.232067510548</v>
+        <v>-83.794466403162</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>7.692307692307</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I17" s="15">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J17" s="15">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K17" s="14">
-        <v>12.903225806451</v>
+        <v>12.121212121212</v>
       </c>
       <c r="L17" s="14">
-        <v>12.903225806451</v>
+        <v>13.846153846153</v>
       </c>
       <c r="M17" s="14">
-        <v>55.555555555555</v>
+        <v>48</v>
       </c>
       <c r="N17" s="14">
-        <v>55.555555555555</v>
+        <v>45.098039215686</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
         <v>-80</v>
       </c>
       <c r="F18" s="15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H18" s="14">
-        <v>-20</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I18" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K18" s="14">
-        <v>-30.952380952381</v>
+        <v>-36.170212765957</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.297872340425</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="M18" s="14">
-        <v>-71</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.394077448747</v>
+        <v>-93.630573248407</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="15">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G19" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H19" s="14">
-        <v>22.5</v>
+        <v>2.439024390243</v>
       </c>
       <c r="I19" s="15">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J19" s="15">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="K19" s="14">
-        <v>21.818181818181</v>
+        <v>15.833333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.176470588235</v>
+        <v>-26.842105263157</v>
       </c>
       <c r="M19" s="14">
-        <v>59.523809523809</v>
+        <v>51.086956521739</v>
       </c>
       <c r="N19" s="14">
-        <v>4.6875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D20" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G20" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H20" s="14">
-        <v>-15.384615384615</v>
+        <v>10.714285714285</v>
       </c>
       <c r="I20" s="15">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J20" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K20" s="14">
-        <v>30.612244897959</v>
+        <v>43.396226415094</v>
       </c>
       <c r="L20" s="14">
-        <v>-14.666666666666</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="M20" s="14">
-        <v>10.344827586206</v>
+        <v>15.151515151515</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.784338896020</v>
+        <v>-91.244239631336</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>31</v>
+      </c>
+      <c r="D21" s="17">
         <v>27</v>
       </c>
-      <c r="D21" s="17">
-        <v>40</v>
-      </c>
       <c r="E21" s="18">
-        <v>-32.5</v>
+        <v>14.814814814814</v>
       </c>
       <c r="F21" s="17">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-3.816793893129</v>
       </c>
       <c r="I21" s="17">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="J21" s="17">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="K21" s="18">
-        <v>13.804713804713</v>
+        <v>12.962962962963</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.920398009950</v>
+        <v>-16.247139588100</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.169590643274</v>
+        <v>-1.612903225806</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.390243902439</v>
+        <v>-79.598662207357</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D24" s="15">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E24" s="14">
-        <v>-19.354838709677</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F24" s="15">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="G24" s="15">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H24" s="14">
-        <v>2.409638554216</v>
+        <v>32.558139534883</v>
       </c>
       <c r="I24" s="15">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="J24" s="15">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="K24" s="14">
-        <v>-2.671755725190</v>
+        <v>2.464788732394</v>
       </c>
       <c r="L24" s="14">
-        <v>-22.492401215805</v>
+        <v>-18.941504178273</v>
       </c>
       <c r="M24" s="14">
-        <v>8.974358974358</v>
+        <v>15.476190476190</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-45.454545454545</v>
+        <v>37.5</v>
       </c>
       <c r="F25" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G25" s="15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.368421052631</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J25" s="15">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K25" s="14">
-        <v>-36.936936936936</v>
+        <v>-31.932773109243</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.571428571428</v>
+        <v>-25.688073394495</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>14.285714285714</v>
+        <v>19.354838709677</v>
       </c>
       <c r="I26" s="15">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J26" s="15">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K26" s="14">
-        <v>20.408163265306</v>
+        <v>19.047619047619</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.8125</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M26" s="14">
-        <v>-29.341317365269</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-85.714285714285</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
         <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>-46.153846153846</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -878,11 +878,11 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
+      </c>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
         <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>-7.142857142857</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J16" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" s="14">
-        <v>41.379310344827</v>
+        <v>34.375</v>
       </c>
       <c r="L16" s="14">
-        <v>-10.869565217391</v>
+        <v>-14</v>
       </c>
       <c r="M16" s="14">
-        <v>-25.454545454545</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.794466403162</v>
+        <v>-83.955223880597</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>22.727272727272</v>
+        <v>12</v>
       </c>
       <c r="I17" s="15">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J17" s="15">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K17" s="14">
-        <v>12.121212121212</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L17" s="14">
-        <v>13.846153846153</v>
+        <v>19.402985074626</v>
       </c>
       <c r="M17" s="14">
-        <v>48</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N17" s="14">
-        <v>45.098039215686</v>
+        <v>40.350877192982</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-45.454545454545</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="15">
         <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="14">
-        <v>-36.170212765957</v>
+        <v>-40</v>
       </c>
       <c r="L18" s="14">
-        <v>-43.396226415094</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="M18" s="14">
-        <v>-71.428571428571</v>
+        <v>-73.451327433628</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.630573248407</v>
+        <v>-94.129158512720</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="F19" s="15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" s="15">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H19" s="14">
-        <v>2.439024390243</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="I19" s="15">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J19" s="15">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="K19" s="14">
-        <v>15.833333333333</v>
+        <v>5.594405594405</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.842105263157</v>
+        <v>-24.5</v>
       </c>
       <c r="M19" s="14">
-        <v>51.086956521739</v>
+        <v>51</v>
       </c>
       <c r="N19" s="14">
-        <v>0</v>
+        <v>2.027027027027</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="14">
-        <v>10.714285714285</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I20" s="15">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J20" s="15">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K20" s="14">
-        <v>43.396226415094</v>
+        <v>38.983050847457</v>
       </c>
       <c r="L20" s="14">
-        <v>-2.564102564102</v>
+        <v>-9.890109890109</v>
       </c>
       <c r="M20" s="14">
-        <v>15.151515151515</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.244239631336</v>
+        <v>-91.313559322033</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>14.814814814814</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.816793893129</v>
+        <v>-16.783216783216</v>
       </c>
       <c r="I21" s="17">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="J21" s="17">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="K21" s="18">
-        <v>12.962962962963</v>
+        <v>7.397260273972</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.247139588100</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.612903225806</v>
+        <v>-5.542168674698</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.598662207357</v>
+        <v>-79.804224626481</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E24" s="14">
-        <v>54.545454545454</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F24" s="15">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G24" s="15">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H24" s="14">
-        <v>32.558139534883</v>
+        <v>10.416666666666</v>
       </c>
       <c r="I24" s="15">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="J24" s="15">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="K24" s="14">
-        <v>2.464788732394</v>
+        <v>-0.322580645161</v>
       </c>
       <c r="L24" s="14">
-        <v>-18.941504178273</v>
+        <v>-18.253968253968</v>
       </c>
       <c r="M24" s="14">
-        <v>15.476190476190</v>
+        <v>14.022140221402</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>37.5</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G25" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H25" s="14">
-        <v>-16.666666666666</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="I25" s="15">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J25" s="15">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.932773109243</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="L25" s="14">
-        <v>-25.688073394495</v>
+        <v>-23.893805309734</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H26" s="14">
-        <v>19.354838709677</v>
+        <v>2.631578947368</v>
       </c>
       <c r="I26" s="15">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="J26" s="15">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="K26" s="14">
-        <v>19.047619047619</v>
+        <v>13.223140495867</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.714285714285</v>
+        <v>-9.868421052631</v>
       </c>
       <c r="M26" s="14">
-        <v>-30.555555555555</v>
+        <v>-30.102040816326</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L28" s="14">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
@@ -920,7 +920,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
         <v>50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J16" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>34.375</v>
+        <v>39.393939393939</v>
       </c>
       <c r="L16" s="14">
-        <v>-14</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-27.118644067796</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.955223880597</v>
+        <v>-83.859649122807</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F17" s="15">
+        <v>21</v>
+      </c>
+      <c r="G17" s="15">
+        <v>21</v>
+      </c>
+      <c r="H17" s="14">
         <v>0</v>
       </c>
-      <c r="F17" s="15">
-        <v>28</v>
-      </c>
-      <c r="G17" s="15">
-        <v>25</v>
-      </c>
-      <c r="H17" s="14">
-        <v>12</v>
-      </c>
       <c r="I17" s="15">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J17" s="15">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K17" s="14">
-        <v>11.111111111111</v>
+        <v>8</v>
       </c>
       <c r="L17" s="14">
-        <v>19.402985074626</v>
+        <v>12.5</v>
       </c>
       <c r="M17" s="14">
-        <v>42.857142857142</v>
+        <v>37.288135593220</v>
       </c>
       <c r="N17" s="14">
-        <v>40.350877192982</v>
+        <v>19.117647058823</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H18" s="14">
-        <v>-66.666666666666</v>
+        <v>-88.461538461538</v>
       </c>
       <c r="I18" s="15">
         <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K18" s="14">
-        <v>-40</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="L18" s="14">
-        <v>-48.275862068965</v>
+        <v>-50.819672131147</v>
       </c>
       <c r="M18" s="14">
-        <v>-73.451327433628</v>
+        <v>-75</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.129158512720</v>
+        <v>-94.614003590664</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>-52.173913043478</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="15">
         <v>40</v>
       </c>
       <c r="G19" s="15">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H19" s="14">
-        <v>-24.528301886792</v>
+        <v>-29.824561403508</v>
       </c>
       <c r="I19" s="15">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="J19" s="15">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="K19" s="14">
-        <v>5.594405594405</v>
+        <v>3.797468354430</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.5</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="M19" s="14">
-        <v>51</v>
+        <v>57.692307692307</v>
       </c>
       <c r="N19" s="14">
-        <v>2.027027027027</v>
+        <v>5.806451612903</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="F20" s="15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="14">
-        <v>11.111111111111</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I20" s="15">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J20" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K20" s="14">
-        <v>38.983050847457</v>
+        <v>32.835820895522</v>
       </c>
       <c r="L20" s="14">
-        <v>-9.890109890109</v>
+        <v>-6.315789473684</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-3.260869565217</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.313559322033</v>
+        <v>-91.384317521781</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.024390243902</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
         <v>143</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.783216783216</v>
+        <v>-27.972027972028</v>
       </c>
       <c r="I21" s="17">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="J21" s="17">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="K21" s="18">
-        <v>7.397260273972</v>
+        <v>4</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.949152542372</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.542168674698</v>
+        <v>-6.094808126410</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.804224626481</v>
+        <v>-80.293699668403</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>-30.769230769230</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="F24" s="15">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G24" s="15">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H24" s="14">
-        <v>10.416666666666</v>
+        <v>-11.818181818181</v>
       </c>
       <c r="I24" s="15">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="J24" s="15">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="K24" s="14">
-        <v>-0.322580645161</v>
+        <v>-4.105571847507</v>
       </c>
       <c r="L24" s="14">
-        <v>-18.253968253968</v>
+        <v>-18.858560794044</v>
       </c>
       <c r="M24" s="14">
-        <v>14.022140221402</v>
+        <v>9.364548494983</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E25" s="14">
-        <v>-28.571428571428</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G25" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H25" s="14">
-        <v>-25.714285714285</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I25" s="15">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J25" s="15">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.746031746031</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.893805309734</v>
+        <v>-29.007633587786</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>114.285714285714</v>
       </c>
       <c r="F26" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H26" s="14">
-        <v>2.631578947368</v>
+        <v>4.878048780487</v>
       </c>
       <c r="I26" s="15">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="J26" s="15">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K26" s="14">
-        <v>13.223140495867</v>
+        <v>18.75</v>
       </c>
       <c r="L26" s="14">
-        <v>-9.868421052631</v>
+        <v>-3.797468354430</v>
       </c>
       <c r="M26" s="14">
-        <v>-30.102040816326</v>
+        <v>-25.853658536585</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>-40</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>12.5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -920,7 +920,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="14">
         <v>50</v>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I16" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J16" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K16" s="14">
-        <v>39.393939393939</v>
+        <v>36.111111111111</v>
       </c>
       <c r="L16" s="14">
-        <v>-23.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M16" s="14">
-        <v>-26.984126984127</v>
+        <v>-30</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.859649122807</v>
+        <v>-83.612040133779</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>112.5</v>
       </c>
       <c r="F17" s="15">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G17" s="15">
         <v>21</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>38.095238095238</v>
       </c>
       <c r="I17" s="15">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="J17" s="15">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="K17" s="14">
-        <v>8</v>
+        <v>21.686746987951</v>
       </c>
       <c r="L17" s="14">
-        <v>12.5</v>
+        <v>24.691358024691</v>
       </c>
       <c r="M17" s="14">
-        <v>37.288135593220</v>
+        <v>57.8125</v>
       </c>
       <c r="N17" s="14">
-        <v>19.117647058823</v>
+        <v>40.277777777777</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
         <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>-88.461538461538</v>
+        <v>-84.210526315789</v>
       </c>
       <c r="I18" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J18" s="15">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K18" s="14">
-        <v>-48.275862068965</v>
+        <v>-47.540983606557</v>
       </c>
       <c r="L18" s="14">
-        <v>-50.819672131147</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M18" s="14">
-        <v>-75</v>
+        <v>-74.4</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.614003590664</v>
+        <v>-94.567062818336</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>16</v>
+      </c>
+      <c r="D19" s="15">
         <v>12</v>
       </c>
-      <c r="D19" s="15">
-        <v>15</v>
-      </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G19" s="15">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H19" s="14">
-        <v>-29.824561403508</v>
+        <v>-18.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="J19" s="15">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K19" s="14">
-        <v>3.797468354430</v>
+        <v>7.058823529411</v>
       </c>
       <c r="L19" s="14">
-        <v>-22.641509433962</v>
+        <v>-16.894977168949</v>
       </c>
       <c r="M19" s="14">
-        <v>57.692307692307</v>
+        <v>61.061946902654</v>
       </c>
       <c r="N19" s="14">
-        <v>5.806451612903</v>
+        <v>10.303030303030</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14">
-        <v>-12.5</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F20" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G20" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H20" s="14">
-        <v>3.846153846153</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I20" s="15">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J20" s="15">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K20" s="14">
-        <v>32.835820895522</v>
+        <v>21.25</v>
       </c>
       <c r="L20" s="14">
-        <v>-6.315789473684</v>
+        <v>-7.619047619047</v>
       </c>
       <c r="M20" s="14">
-        <v>-3.260869565217</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.384317521781</v>
+        <v>-91.339285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>-34.285714285714</v>
+        <v>17.948717948717</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G21" s="17">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.972027972028</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="I21" s="17">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="J21" s="17">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="K21" s="18">
-        <v>4</v>
+        <v>6.378132118451</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.948717948717</v>
+        <v>-14.311926605504</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.094808126410</v>
+        <v>-1.476793248945</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.293699668403</v>
+        <v>-79.336283185840</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
@@ -1210,7 +1210,7 @@
         <v>-37.5</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D24" s="15">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E24" s="14">
-        <v>-35.483870967741</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="F24" s="15">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G24" s="15">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="14">
-        <v>-11.818181818181</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="I24" s="15">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="J24" s="15">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="K24" s="14">
-        <v>-4.105571847507</v>
+        <v>-4.619565217391</v>
       </c>
       <c r="L24" s="14">
-        <v>-18.858560794044</v>
+        <v>-17.798594847775</v>
       </c>
       <c r="M24" s="14">
-        <v>9.364548494983</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-41.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F25" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G25" s="15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H25" s="14">
-        <v>-23.684210526315</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="I25" s="15">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J25" s="15">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="K25" s="14">
-        <v>-32.608695652173</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="L25" s="14">
-        <v>-29.007633587786</v>
+        <v>-25.179856115107</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>114.285714285714</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G26" s="15">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H26" s="14">
-        <v>4.878048780487</v>
+        <v>18.421052631578</v>
       </c>
       <c r="I26" s="15">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="J26" s="15">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K26" s="14">
-        <v>18.75</v>
+        <v>19.117647058823</v>
       </c>
       <c r="L26" s="14">
-        <v>-3.797468354430</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.853658536585</v>
+        <v>-25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>-40</v>
       </c>
       <c r="L27" s="14">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
         <v>0</v>
       </c>
       <c r="F28" s="15">
+        <v>5</v>
+      </c>
+      <c r="G28" s="15">
         <v>4</v>
       </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-33.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L28" s="14">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,43 +854,43 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="M14" s="14">
+      <c r="L14" s="15">
         <v>-100</v>
       </c>
-      <c r="N14" s="14">
+      <c r="M14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -899,239 +899,239 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="14">
         <v>6</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>9</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="L15" s="14">
-        <v>-25</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="L15" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M15" s="15">
         <v>50</v>
       </c>
-      <c r="N15" s="14">
-        <v>-25</v>
+      <c r="N15" s="15">
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
-        <v>14</v>
-      </c>
-      <c r="G16" s="15">
-        <v>10</v>
-      </c>
-      <c r="H16" s="14">
+      <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>13</v>
+      </c>
+      <c r="G16" s="14">
+        <v>11</v>
+      </c>
+      <c r="H16" s="15">
+        <v>18.181818181818</v>
+      </c>
+      <c r="I16" s="14">
+        <v>54</v>
+      </c>
+      <c r="J16" s="14">
         <v>40</v>
       </c>
-      <c r="I16" s="15">
-        <v>49</v>
-      </c>
-      <c r="J16" s="15">
-        <v>36</v>
-      </c>
-      <c r="K16" s="14">
-        <v>36.111111111111</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-30</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-83.612040133779</v>
+      <c r="K16" s="15">
+        <v>35</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-15.625</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-29.870129870129</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-83.072100313479</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>17</v>
-      </c>
-      <c r="D17" s="15">
-        <v>8</v>
-      </c>
-      <c r="E17" s="14">
-        <v>112.5</v>
-      </c>
-      <c r="F17" s="15">
-        <v>29</v>
-      </c>
-      <c r="G17" s="15">
-        <v>21</v>
-      </c>
-      <c r="H17" s="14">
-        <v>38.095238095238</v>
-      </c>
-      <c r="I17" s="15">
-        <v>101</v>
-      </c>
-      <c r="J17" s="15">
-        <v>83</v>
-      </c>
-      <c r="K17" s="14">
-        <v>21.686746987951</v>
-      </c>
-      <c r="L17" s="14">
-        <v>24.691358024691</v>
-      </c>
-      <c r="M17" s="14">
-        <v>57.8125</v>
-      </c>
-      <c r="N17" s="14">
-        <v>40.277777777777</v>
+      <c r="C17" s="14">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14">
+        <v>6</v>
+      </c>
+      <c r="E17" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="F17" s="14">
+        <v>32</v>
+      </c>
+      <c r="G17" s="14">
+        <v>23</v>
+      </c>
+      <c r="H17" s="15">
+        <v>39.130434782608</v>
+      </c>
+      <c r="I17" s="14">
+        <v>108</v>
+      </c>
+      <c r="J17" s="14">
+        <v>89</v>
+      </c>
+      <c r="K17" s="15">
+        <v>21.348314606741</v>
+      </c>
+      <c r="L17" s="15">
+        <v>20</v>
+      </c>
+      <c r="M17" s="15">
+        <v>56.521739130434</v>
+      </c>
+      <c r="N17" s="15">
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
+      <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F18" s="15">
-        <v>3</v>
-      </c>
-      <c r="G18" s="15">
-        <v>19</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-84.210526315789</v>
-      </c>
-      <c r="I18" s="15">
-        <v>32</v>
-      </c>
-      <c r="J18" s="15">
-        <v>61</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-47.540983606557</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-52.941176470588</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-74.4</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-94.567062818336</v>
+      <c r="G18" s="14">
+        <v>16</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-81.25</v>
+      </c>
+      <c r="I18" s="14">
+        <v>33</v>
+      </c>
+      <c r="J18" s="14">
+        <v>63</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-47.619047619047</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-54.794520547945</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-74.809160305343</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-94.770206022187</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>16</v>
-      </c>
-      <c r="D19" s="15">
-        <v>12</v>
-      </c>
-      <c r="E19" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="F19" s="15">
-        <v>49</v>
-      </c>
-      <c r="G19" s="15">
-        <v>60</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-18.333333333333</v>
-      </c>
-      <c r="I19" s="15">
-        <v>182</v>
-      </c>
-      <c r="J19" s="15">
-        <v>170</v>
-      </c>
-      <c r="K19" s="14">
-        <v>7.058823529411</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-16.894977168949</v>
-      </c>
-      <c r="M19" s="14">
-        <v>61.061946902654</v>
-      </c>
-      <c r="N19" s="14">
-        <v>10.303030303030</v>
+      <c r="C19" s="14">
+        <v>13</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8</v>
+      </c>
+      <c r="E19" s="15">
+        <v>62.5</v>
+      </c>
+      <c r="F19" s="14">
+        <v>55</v>
+      </c>
+      <c r="G19" s="14">
+        <v>58</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-5.172413793103</v>
+      </c>
+      <c r="I19" s="14">
+        <v>196</v>
+      </c>
+      <c r="J19" s="14">
+        <v>178</v>
+      </c>
+      <c r="K19" s="15">
+        <v>10.112359550561</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-16.949152542372</v>
+      </c>
+      <c r="M19" s="15">
+        <v>68.965517241379</v>
+      </c>
+      <c r="N19" s="15">
+        <v>7.103825136612</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <v>8</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="14">
         <v>13</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="15">
         <v>-38.461538461538</v>
       </c>
-      <c r="F20" s="15">
-        <v>33</v>
-      </c>
-      <c r="G20" s="15">
-        <v>31</v>
-      </c>
-      <c r="H20" s="14">
-        <v>6.451612903225</v>
-      </c>
-      <c r="I20" s="15">
-        <v>97</v>
-      </c>
-      <c r="J20" s="15">
-        <v>80</v>
-      </c>
-      <c r="K20" s="14">
-        <v>21.25</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-7.619047619047</v>
-      </c>
-      <c r="M20" s="14">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-91.339285714285</v>
+      <c r="F20" s="14">
+        <v>29</v>
+      </c>
+      <c r="G20" s="14">
+        <v>40</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-27.5</v>
+      </c>
+      <c r="I20" s="14">
+        <v>105</v>
+      </c>
+      <c r="J20" s="14">
+        <v>93</v>
+      </c>
+      <c r="K20" s="15">
+        <v>12.903225806451</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-6.25</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-5.405405405405</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-91.213389121338</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>17.948717948717</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G21" s="17">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.859154929577</v>
+        <v>-11.409395973154</v>
       </c>
       <c r="I21" s="17">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="J21" s="17">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="K21" s="18">
-        <v>6.378132118451</v>
+        <v>6.131078224101</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.311926605504</v>
+        <v>-14.188034188034</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.476793248945</v>
+        <v>-1.375245579567</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.336283185840</v>
+        <v>-79.298969072165</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,38 +1182,38 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I22" s="14">
         <v>5</v>
       </c>
-      <c r="J22" s="15">
-        <v>5</v>
-      </c>
-      <c r="K22" s="14">
-        <v>0</v>
-      </c>
-      <c r="L22" s="14">
+      <c r="J22" s="14">
+        <v>6</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="L22" s="15">
         <v>-37.5</v>
       </c>
-      <c r="M22" s="14">
-        <v>-16.666666666666</v>
+      <c r="M22" s="15">
+        <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1245,303 +1245,303 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>26</v>
-      </c>
-      <c r="D24" s="15">
-        <v>27</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-3.703703703703</v>
-      </c>
-      <c r="F24" s="15">
-        <v>94</v>
-      </c>
-      <c r="G24" s="15">
-        <v>106</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-11.320754716981</v>
-      </c>
-      <c r="I24" s="15">
-        <v>351</v>
-      </c>
-      <c r="J24" s="15">
-        <v>368</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-4.619565217391</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-17.798594847775</v>
-      </c>
-      <c r="M24" s="14">
-        <v>8.333333333333</v>
+      <c r="C24" s="14">
+        <v>32</v>
+      </c>
+      <c r="D24" s="14">
+        <v>12</v>
+      </c>
+      <c r="E24" s="15">
+        <v>166.666666666667</v>
+      </c>
+      <c r="F24" s="14">
+        <v>91</v>
+      </c>
+      <c r="G24" s="14">
+        <v>96</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-5.208333333333</v>
+      </c>
+      <c r="I24" s="14">
+        <v>382</v>
+      </c>
+      <c r="J24" s="14">
+        <v>380</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.526315789473</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-15.673289183223</v>
+      </c>
+      <c r="M24" s="15">
+        <v>11.046511627907</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>12</v>
-      </c>
-      <c r="D25" s="15">
-        <v>10</v>
-      </c>
-      <c r="E25" s="14">
-        <v>20</v>
-      </c>
-      <c r="F25" s="15">
-        <v>34</v>
-      </c>
-      <c r="G25" s="15">
-        <v>37</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-8.108108108108</v>
-      </c>
-      <c r="I25" s="15">
-        <v>104</v>
-      </c>
-      <c r="J25" s="15">
-        <v>148</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-29.729729729729</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-25.179856115107</v>
+      <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
+        <v>7</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="F25" s="14">
+        <v>28</v>
+      </c>
+      <c r="G25" s="14">
+        <v>36</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="I25" s="14">
+        <v>109</v>
+      </c>
+      <c r="J25" s="14">
+        <v>155</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-29.677419354838</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-27.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>10</v>
-      </c>
-      <c r="D26" s="15">
-        <v>8</v>
-      </c>
-      <c r="E26" s="14">
+      <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
+        <v>4</v>
+      </c>
+      <c r="E26" s="15">
+        <v>225</v>
+      </c>
+      <c r="F26" s="14">
+        <v>51</v>
+      </c>
+      <c r="G26" s="14">
+        <v>35</v>
+      </c>
+      <c r="H26" s="15">
+        <v>45.714285714285</v>
+      </c>
+      <c r="I26" s="14">
+        <v>175</v>
+      </c>
+      <c r="J26" s="14">
+        <v>140</v>
+      </c>
+      <c r="K26" s="15">
         <v>25</v>
       </c>
-      <c r="F26" s="15">
-        <v>45</v>
-      </c>
-      <c r="G26" s="15">
-        <v>38</v>
-      </c>
-      <c r="H26" s="14">
-        <v>18.421052631578</v>
-      </c>
-      <c r="I26" s="15">
-        <v>162</v>
-      </c>
-      <c r="J26" s="15">
-        <v>136</v>
-      </c>
-      <c r="K26" s="14">
-        <v>19.117647058823</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-5.813953488372</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-25</v>
+      <c r="L26" s="15">
+        <v>-4.371584699453</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-22.222222222222</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="15">
+        <v>22</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="H27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="15">
-        <v>6</v>
-      </c>
-      <c r="J27" s="15">
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="14">
+        <v>7</v>
+      </c>
+      <c r="J27" s="14">
         <v>10</v>
       </c>
-      <c r="K27" s="14">
-        <v>-40</v>
-      </c>
-      <c r="L27" s="14">
-        <v>-33.333333333333</v>
+      <c r="K27" s="15">
+        <v>-30</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-30</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>5</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>4</v>
       </c>
-      <c r="H28" s="14">
-        <v>25</v>
-      </c>
-      <c r="I28" s="15">
+      <c r="E28" s="15">
+        <v>-75</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I28" s="14">
         <v>12</v>
       </c>
-      <c r="J28" s="15">
-        <v>17</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-29.411764705882</v>
-      </c>
-      <c r="L28" s="14">
+      <c r="J28" s="14">
+        <v>21</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L28" s="15">
         <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="15">
+      <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="15">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="K29" s="14">
+      <c r="E29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="14">
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
         <v>0</v>
       </c>
+      <c r="I29" s="14">
+        <v>2</v>
+      </c>
+      <c r="J29" s="14">
+        <v>2</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
+      </c>
+      <c r="L29" s="15">
+        <v>100</v>
+      </c>
       <c r="M29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-83.333333333333</v>
+        <v>22</v>
+      </c>
+      <c r="N29" s="15">
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="15">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="K30" s="14">
+      <c r="E30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="14">
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
         <v>0</v>
       </c>
+      <c r="I30" s="14">
+        <v>2</v>
+      </c>
+      <c r="J30" s="14">
+        <v>2</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
+      </c>
+      <c r="L30" s="15">
+        <v>100</v>
+      </c>
       <c r="M30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="14">
-        <v>-83.333333333333</v>
+        <v>22</v>
+      </c>
+      <c r="N30" s="15">
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,25 +1564,25 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="15">
+        <v>22</v>
+      </c>
+      <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>3</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,38 +1610,38 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="14">
         <v>1</v>
       </c>
-      <c r="E33" s="14">
+      <c r="H33" s="15">
         <v>-100</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="15">
+      <c r="I33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="H33" s="14">
+      <c r="K33" s="15">
         <v>-100</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="15">
-        <v>1</v>
-      </c>
-      <c r="K33" s="14">
-        <v>-100</v>
-      </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1742,63 +1742,63 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>11</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>19</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>7</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>5</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>5</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>0</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-28.571428571428</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-73.684210526315</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-54.545454545454</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="15">
         <v>21</v>
       </c>
-      <c r="E40" s="15">
+      <c r="C40" s="14">
         <v>21</v>
       </c>
-      <c r="G40" s="15">
+      <c r="E40" s="14">
+        <v>21</v>
+      </c>
+      <c r="G40" s="14">
         <v>24</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>15</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>34</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>126.666666666667</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>41.666666666666</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>61.904761904761</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>61.904761904761</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1307</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1027</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>490</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>359</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>159</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-55.710306406685</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-67.551020408163</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-84.518013631937</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-87.834736036725</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>279</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>305</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>261</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>262</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>295</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>12.595419847328</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>13.026819923371</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-3.278688524590</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>5.734767025089</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>2562</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1955</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>1024</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>790</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>166</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-78.987341772151</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-83.7890625</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-91.508951406649</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-93.520686963309</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>884</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>678</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>485</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>551</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>702</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>27.404718693284</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>44.742268041237</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>3.539823008849</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-20.588235294117</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>4443</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>3418</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>1374</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>892</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>386</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-56.726457399103</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-71.906841339155</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-88.706846108835</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-91.312176457348</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>22</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>18.181818181818</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
         <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>35</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.625</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M16" s="15">
-        <v>-29.870129870129</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.072100313479</v>
+        <v>-83.976261127596</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>-70</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>39.130434782608</v>
+        <v>7.407407407407</v>
       </c>
       <c r="I17" s="14">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J17" s="14">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K17" s="15">
-        <v>21.348314606741</v>
+        <v>13.131313131313</v>
       </c>
       <c r="L17" s="15">
-        <v>20</v>
+        <v>17.894736842105</v>
       </c>
       <c r="M17" s="15">
-        <v>56.521739130434</v>
+        <v>49.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>33.333333333333</v>
+        <v>27.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F18" s="14">
+        <v>4</v>
+      </c>
+      <c r="G18" s="14">
+        <v>18</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="I18" s="14">
+        <v>34</v>
+      </c>
+      <c r="J18" s="14">
+        <v>68</v>
+      </c>
+      <c r="K18" s="15">
         <v>-50</v>
       </c>
-      <c r="F18" s="14">
-        <v>3</v>
-      </c>
-      <c r="G18" s="14">
-        <v>16</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-81.25</v>
-      </c>
-      <c r="I18" s="14">
-        <v>33</v>
-      </c>
-      <c r="J18" s="14">
-        <v>63</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-47.619047619047</v>
-      </c>
       <c r="L18" s="15">
-        <v>-54.794520547945</v>
+        <v>-55.844155844155</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.809160305343</v>
+        <v>-75.182481751824</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.770206022187</v>
+        <v>-94.992636229749</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>62.5</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F19" s="14">
         <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.172413793103</v>
+        <v>5.769230769230</v>
       </c>
       <c r="I19" s="14">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="J19" s="14">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="K19" s="15">
-        <v>10.112359550561</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.949152542372</v>
+        <v>-15.447154471544</v>
       </c>
       <c r="M19" s="15">
-        <v>68.965517241379</v>
+        <v>65.079365079365</v>
       </c>
       <c r="N19" s="15">
-        <v>7.103825136612</v>
+        <v>5.583756345177</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-38.461538461538</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G20" s="14">
         <v>40</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.5</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="J20" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K20" s="15">
-        <v>12.903225806451</v>
+        <v>13.131313131313</v>
       </c>
       <c r="L20" s="15">
-        <v>-6.25</v>
+        <v>-4.273504273504</v>
       </c>
       <c r="M20" s="15">
-        <v>-5.405405405405</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.213389121338</v>
+        <v>-91.290824261275</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="F21" s="17">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17">
         <v>149</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.409395973154</v>
+        <v>-12.751677852349</v>
       </c>
       <c r="I21" s="17">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="J21" s="17">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="K21" s="18">
-        <v>6.131078224101</v>
+        <v>2.529182879377</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.188034188034</v>
+        <v>-13.747954173486</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.375245579567</v>
+        <v>-3.125</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.298969072165</v>
+        <v>-79.769673704414</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1207,13 +1207,13 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M22" s="15">
         <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>166.666666666667</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14">
         <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.208333333333</v>
+        <v>3.125</v>
       </c>
       <c r="I24" s="14">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="J24" s="14">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="K24" s="15">
-        <v>0.526315789473</v>
+        <v>-0.246305418719</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.673289183223</v>
+        <v>-13.276231263383</v>
       </c>
       <c r="M24" s="15">
-        <v>11.046511627907</v>
+        <v>11.878453038674</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.571428571428</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.222222222222</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="I25" s="14">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.677419354838</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>225</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>45.714285714285</v>
+        <v>55.882352941176</v>
       </c>
       <c r="I26" s="14">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="J26" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K26" s="15">
-        <v>25</v>
+        <v>21.935483870967</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.371584699453</v>
+        <v>-5.025125628140</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.222222222222</v>
+        <v>-24.4</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,38 +1387,38 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>22</v>
+      <c r="H27" s="15">
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L27" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1444,36 +1444,36 @@
         <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-42.857142857142</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L28" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1497,24 +1497,24 @@
         <v>100</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>100</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1579,10 +1579,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1635,13 +1635,13 @@
         <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-104pct.xlsx
+++ b/data/source/weekly/cs-en-us-104pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L15" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>10</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>28.571428571428</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-18.181818181818</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.333333333333</v>
+        <v>-33.720930232558</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.976261127596</v>
+        <v>-83.620689655172</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
         <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-70</v>
+        <v>-10</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>7.407407407407</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K17" s="15">
-        <v>13.131313131313</v>
+        <v>11.926605504587</v>
       </c>
       <c r="L17" s="15">
-        <v>17.894736842105</v>
+        <v>18.446601941747</v>
       </c>
       <c r="M17" s="15">
-        <v>49.333333333333</v>
+        <v>50.617283950617</v>
       </c>
       <c r="N17" s="15">
-        <v>27.272727272727</v>
+        <v>29.787234042553</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>400</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-77.777777777777</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L18" s="15">
-        <v>-55.844155844155</v>
+        <v>-50.632911392405</v>
       </c>
       <c r="M18" s="15">
-        <v>-75.182481751824</v>
+        <v>-72.916666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.992636229749</v>
+        <v>-94.568245125348</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.411764705882</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H19" s="15">
-        <v>5.769230769230</v>
+        <v>13.725490196078</v>
       </c>
       <c r="I19" s="14">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="J19" s="14">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="K19" s="15">
-        <v>6.666666666666</v>
+        <v>7.177033492822</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.447154471544</v>
+        <v>-12.156862745098</v>
       </c>
       <c r="M19" s="15">
-        <v>65.079365079365</v>
+        <v>67.164179104477</v>
       </c>
       <c r="N19" s="15">
-        <v>5.583756345177</v>
+        <v>4.186046511627</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>16.666666666666</v>
+        <v>125</v>
       </c>
       <c r="F20" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I20" s="14">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J20" s="14">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K20" s="15">
-        <v>13.131313131313</v>
+        <v>17.475728155339</v>
       </c>
       <c r="L20" s="15">
-        <v>-4.273504273504</v>
+        <v>-5.46875</v>
       </c>
       <c r="M20" s="15">
-        <v>-5.882352941176</v>
+        <v>-1.626016260162</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.290824261275</v>
+        <v>-91.023738872403</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.024390243902</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G21" s="17">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.751677852349</v>
+        <v>2.040816326530</v>
       </c>
       <c r="I21" s="17">
-        <v>527</v>
+        <v>571</v>
       </c>
       <c r="J21" s="17">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="K21" s="18">
-        <v>2.529182879377</v>
+        <v>4.387568555758</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.747954173486</v>
+        <v>-11.335403726708</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.125</v>
+        <v>-0.522648083623</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.769673704414</v>
+        <v>-79.175784099197</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,13 +1201,13 @@
         <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>-28.571428571428</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
         <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.846153846153</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>3.125</v>
+        <v>6.593406593406</v>
       </c>
       <c r="I24" s="14">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="J24" s="14">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.246305418719</v>
+        <v>-2.314814814814</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.276231263383</v>
+        <v>-14.574898785425</v>
       </c>
       <c r="M24" s="15">
-        <v>11.878453038674</v>
+        <v>10.471204188481</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.512820512820</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J25" s="14">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.090909090909</v>
+        <v>-27.745664739884</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.529411764705</v>
+        <v>-23.312883435582</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-6.666666666666</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>55.882352941176</v>
+        <v>28.947368421052</v>
       </c>
       <c r="I26" s="14">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J26" s="14">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K26" s="15">
-        <v>21.935483870967</v>
+        <v>21.084337349397</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.025125628140</v>
+        <v>-3.365384615384</v>
       </c>
       <c r="M26" s="15">
-        <v>-24.4</v>
+        <v>-23.574144486692</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>0</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-27.272727272727</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="15">
-        <v>-27.272727272727</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="I28" s="14">
         <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>-40.909090909090</v>
+        <v>-48</v>
       </c>
       <c r="L28" s="15">
         <v>8.333333333333</v>
@@ -1576,7 +1576,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,23 +1616,23 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>
